--- a/site/leagues/betclic/2026_2027/xlsx/context_packs/context_pack_UDO.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/context_packs/context_pack_UDO.xlsx
@@ -17,12 +17,12 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$C$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'context_alerts'!$A$1:$B$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'team_splits'!$A$1:$I$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'context_alerts'!$A$1:$B$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'team_splits'!$A$1:$I$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'key_players_context'!$A$1:$M$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'team_periods'!$A$1:$K$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'key_players_periods'!$A$1:$Q$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'game_log'!$A$1:$G$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'game_log'!$A$1:$G$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -544,7 +544,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>79.0</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>87.0</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>-8.0</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>-8.0</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Q1 (14)</t>
+          <t>Q1 (3)</t>
         </is>
       </c>
     </row>
@@ -659,7 +659,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Q4 (-5)</t>
+          <t>Q4 (-4.5)</t>
         </is>
       </c>
     </row>
@@ -675,11 +675,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -697,12 +697,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>períodos</t>
+          <t>resultado</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Melhor período: Q1 (14)</t>
+          <t>Diff médio em vitórias: 9 | em derrotas: -25</t>
         </is>
       </c>
     </row>
@@ -714,12 +714,36 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Pior período: Q4 (-5)</t>
+          <t>Melhor período: Q1 (3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>períodos</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Pior período: Q4 (-4.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>player swing</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>G. Powell sobe mais em vitórias (12 ppg).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B3"/>
+  <autoFilter ref="A1:B5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -730,7 +754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -799,33 +823,66 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>67</v>
+      </c>
+      <c r="E2" t="n">
+        <v>92</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-25</v>
+      </c>
+      <c r="G2" t="n">
+        <v>67</v>
+      </c>
+      <c r="H2" t="n">
+        <v>92</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>W</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="n">
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
         <v>91</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E3" t="n">
         <v>82</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F3" t="n">
         <v>9</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G3" t="n">
         <v>91</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H3" t="n">
         <v>82</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I3" t="n">
         <v>9</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I2"/>
+  <autoFilter ref="A1:I3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -931,13 +988,13 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>18</v>
+        <v>20.4</v>
       </c>
       <c r="F2" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="H2" t="n">
         <v>16</v>
@@ -945,213 +1002,261 @@
       <c r="I2" t="n">
         <v>4</v>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="J2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-8</v>
+      </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. Rodger</t>
+          <t>S. Victo</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>22.7</v>
+        <v>19.4</v>
       </c>
       <c r="F3" t="n">
+        <v>7</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="n">
         <v>14</v>
       </c>
-      <c r="G3" t="n">
-        <v>20</v>
-      </c>
-      <c r="H3" t="n">
-        <v>14</v>
-      </c>
-      <c r="I3" t="n">
-        <v>20</v>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="J3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-8</v>
+      </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. Nixon</t>
+          <t>C. Rodger</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>19.6</v>
+        <v>21.3</v>
       </c>
       <c r="F4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="J4" t="n">
+        <v>6</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-18</v>
+      </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. Morgan</t>
+          <t>J. Turner</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>27.1</v>
+        <v>27</v>
       </c>
       <c r="F5" t="n">
-        <v>12</v>
+        <v>8.5</v>
       </c>
       <c r="G5" t="n">
-        <v>14</v>
+        <v>-14.5</v>
       </c>
       <c r="H5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I5" t="n">
-        <v>14</v>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>7</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-29</v>
+      </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. Victo</t>
+          <t>J. Aramburu</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>22.3</v>
+        <v>22.9</v>
       </c>
       <c r="F6" t="n">
-        <v>12</v>
+        <v>7.5</v>
       </c>
       <c r="G6" t="n">
-        <v>14</v>
+        <v>-10.5</v>
       </c>
       <c r="H6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I6" t="n">
-        <v>14</v>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>7</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-21</v>
+      </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. Turner</t>
+          <t>T. Dias</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>29.2</v>
+        <v>13.9</v>
       </c>
       <c r="F7" t="n">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H7" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-6</v>
+      </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. Aramburu</t>
+          <t>P. Nixon</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
-        <v>23</v>
+        <v>24.3</v>
       </c>
       <c r="F8" t="n">
-        <v>8</v>
+        <v>14.5</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="H8" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="J8" t="n">
+        <v>16</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-24</v>
+      </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>-3</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. Araujo</t>
+          <t>M. Morgan</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
-        <v>18.3</v>
+        <v>28.3</v>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>14.5</v>
       </c>
       <c r="G9" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="I9" t="n">
-        <v>-3</v>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="J9" t="n">
+        <v>17</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-16</v>
+      </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>-5</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:M9"/>
@@ -1260,25 +1365,25 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="G2" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="H2" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I2" t="n">
-        <v>34</v>
+        <v>23.5</v>
       </c>
       <c r="J2" t="n">
-        <v>20</v>
+        <v>20.5</v>
       </c>
       <c r="K2" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -1303,25 +1408,25 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="G3" t="n">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="I3" t="n">
         <v>19</v>
       </c>
       <c r="J3" t="n">
-        <v>19</v>
+        <v>21.5</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="4">
@@ -1346,25 +1451,25 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="G4" t="n">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="I4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J4" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="5">
@@ -1389,25 +1494,25 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="G5" t="n">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="H5" t="n">
-        <v>-5</v>
+        <v>-9</v>
       </c>
       <c r="I5" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="J5" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K5" t="n">
-        <v>-5</v>
+        <v>-4.5</v>
       </c>
     </row>
   </sheetData>
@@ -1534,105 +1639,105 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>G. Powell</t>
+          <t>M. Morgan</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O2" t="n">
         <v>2</v>
       </c>
-      <c r="D2" t="n">
-        <v>6</v>
-      </c>
-      <c r="E2" t="n">
+      <c r="P2" t="n">
         <v>2</v>
       </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. Rodger</t>
+          <t>P. Nixon</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K3" t="n">
         <v>2</v>
       </c>
-      <c r="G3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" t="n">
-        <v>3</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -1644,100 +1749,108 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. Nixon</t>
+          <t>C. Rodger</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C4" t="n">
         <v>2</v>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.5</v>
+      </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. Morgan</t>
+          <t>G. Powell</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
         <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="O5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1746,53 +1859,53 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. Victo</t>
+          <t>J. Turner</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="P6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1801,53 +1914,53 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. Turner</t>
+          <t>J. Aramburu</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1856,95 +1969,111 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. Aramburu</t>
+          <t>S. Victo</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. Araujo</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
+          <t>T. Dias</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.5</v>
+      </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1959,7 +2088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2037,8 +2166,37 @@
         <v>9</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2922732</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SL Benfica</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>67</v>
+      </c>
+      <c r="F3" t="n">
+        <v>92</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-25</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G2"/>
+  <autoFilter ref="A1:G3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/site/leagues/betclic/2026_2027/xlsx/context_packs/context_pack_UDO.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/context_packs/context_pack_UDO.xlsx
@@ -17,12 +17,12 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$C$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'context_alerts'!$A$1:$B$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'team_splits'!$A$1:$I$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'context_alerts'!$A$1:$B$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'team_splits'!$A$1:$I$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'key_players_context'!$A$1:$M$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'team_periods'!$A$1:$K$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'key_players_periods'!$A$1:$Q$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'game_log'!$A$1:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'game_log'!$A$1:$G$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -544,7 +544,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>87.3</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.7</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-8.0</t>
+          <t>2.7</t>
         </is>
       </c>
     </row>
@@ -610,7 +610,11 @@
           <t>diff_casa</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>24.0</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -642,7 +646,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Q1 (3)</t>
+          <t>Q2 (6.3)</t>
         </is>
       </c>
     </row>
@@ -659,7 +663,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Q4 (-4.5)</t>
+          <t>Q4 (-4)</t>
         </is>
       </c>
     </row>
@@ -675,7 +679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -697,24 +701,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>resultado</t>
+          <t>home/away</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Diff médio em vitórias: 9 | em derrotas: -25</t>
+          <t>Diff médio casa: 24 | fora: -8</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>períodos</t>
+          <t>resultado</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Melhor período: Q1 (3)</t>
+          <t>Diff médio em vitórias: 16.5 | em derrotas: -25</t>
         </is>
       </c>
     </row>
@@ -726,24 +730,36 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pior período: Q4 (-4.5)</t>
+          <t>Melhor período: Q2 (6.3)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>períodos</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Pior período: Q4 (-4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>player swing</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>G. Powell sobe mais em vitórias (12 ppg).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B5"/>
+  <autoFilter ref="A1:B6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -754,7 +770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -881,8 +897,41 @@
         <v>9</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>104</v>
+      </c>
+      <c r="E4" t="n">
+        <v>80</v>
+      </c>
+      <c r="F4" t="n">
+        <v>24</v>
+      </c>
+      <c r="G4" t="n">
+        <v>104</v>
+      </c>
+      <c r="H4" t="n">
+        <v>80</v>
+      </c>
+      <c r="I4" t="n">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I3"/>
+  <autoFilter ref="A1:I4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -984,9 +1033,15 @@
           <t>G. Powell</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+      <c r="B2" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="C2" t="n">
+        <v>16</v>
+      </c>
+      <c r="D2" t="n">
+        <v>15</v>
+      </c>
       <c r="E2" t="n">
         <v>20.4</v>
       </c>
@@ -1000,7 +1055,7 @@
         <v>16</v>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>9.5</v>
       </c>
       <c r="J2" t="n">
         <v>4</v>
@@ -1008,7 +1063,9 @@
       <c r="K2" t="n">
         <v>-8</v>
       </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>6</v>
+      </c>
       <c r="M2" t="n">
         <v>12</v>
       </c>
@@ -1016,71 +1073,87 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. Victo</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
+          <t>C. Rodger</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="C3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D3" t="n">
+        <v>17</v>
+      </c>
       <c r="E3" t="n">
-        <v>19.4</v>
+        <v>21.3</v>
       </c>
       <c r="F3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I3" t="n">
-        <v>14</v>
+        <v>18.5</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K3" t="n">
-        <v>-8</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
+        <v>-18</v>
+      </c>
+      <c r="L3" t="n">
+        <v>6</v>
+      </c>
       <c r="M3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. Rodger</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
+          <t>S. Victo</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="C4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4</v>
+      </c>
       <c r="E4" t="n">
-        <v>21.3</v>
+        <v>19.4</v>
       </c>
       <c r="F4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>14</v>
+        <v>9.5</v>
       </c>
       <c r="I4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="J4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>-18</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
+        <v>-8</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
       <c r="M4" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="5">
@@ -1089,9 +1162,15 @@
           <t>J. Turner</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+      <c r="B5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C5" t="n">
+        <v>16</v>
+      </c>
+      <c r="D5" t="n">
+        <v>20</v>
+      </c>
       <c r="E5" t="n">
         <v>27</v>
       </c>
@@ -1102,10 +1181,10 @@
         <v>-14.5</v>
       </c>
       <c r="H5" t="n">
+        <v>13</v>
+      </c>
+      <c r="I5" t="n">
         <v>10</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>7</v>
@@ -1113,9 +1192,11 @@
       <c r="K5" t="n">
         <v>-29</v>
       </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>7.5</v>
+      </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -1124,9 +1205,15 @@
           <t>J. Aramburu</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
+      <c r="B6" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="C6" t="n">
+        <v>12</v>
+      </c>
+      <c r="D6" t="n">
+        <v>16</v>
+      </c>
       <c r="E6" t="n">
         <v>22.9</v>
       </c>
@@ -1137,10 +1224,10 @@
         <v>-10.5</v>
       </c>
       <c r="H6" t="n">
+        <v>10</v>
+      </c>
+      <c r="I6" t="n">
         <v>8</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>7</v>
@@ -1148,79 +1235,97 @@
       <c r="K6" t="n">
         <v>-21</v>
       </c>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>4.5</v>
+      </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. Dias</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
+          <t>P. Nixon</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="C7" t="n">
+        <v>20</v>
+      </c>
+      <c r="D7" t="n">
+        <v>30</v>
+      </c>
       <c r="E7" t="n">
-        <v>13.9</v>
+        <v>24.3</v>
       </c>
       <c r="F7" t="n">
-        <v>2.5</v>
+        <v>14.5</v>
       </c>
       <c r="G7" t="n">
-        <v>-1</v>
+        <v>-12</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>16.5</v>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="K7" t="n">
-        <v>-6</v>
-      </c>
-      <c r="L7" t="inlineStr"/>
+        <v>-24</v>
+      </c>
+      <c r="L7" t="n">
+        <v>5.5</v>
+      </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. Nixon</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
+          <t>T. Dias</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
       <c r="E8" t="n">
-        <v>24.3</v>
+        <v>13.9</v>
       </c>
       <c r="F8" t="n">
-        <v>14.5</v>
+        <v>2.5</v>
       </c>
       <c r="G8" t="n">
-        <v>-12</v>
+        <v>-1</v>
       </c>
       <c r="H8" t="n">
-        <v>13</v>
+        <v>2.5</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>-24</v>
-      </c>
-      <c r="L8" t="inlineStr"/>
+        <v>-6</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-0.5</v>
+      </c>
       <c r="M8" t="n">
-        <v>-3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="9">
@@ -1229,9 +1334,15 @@
           <t>M. Morgan</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+      <c r="B9" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="C9" t="n">
+        <v>9</v>
+      </c>
+      <c r="D9" t="n">
+        <v>25</v>
+      </c>
       <c r="E9" t="n">
         <v>28.3</v>
       </c>
@@ -1242,10 +1353,10 @@
         <v>-1</v>
       </c>
       <c r="H9" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="I9" t="n">
-        <v>14</v>
+        <v>19.5</v>
       </c>
       <c r="J9" t="n">
         <v>17</v>
@@ -1253,9 +1364,11 @@
       <c r="K9" t="n">
         <v>-16</v>
       </c>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>-5.5</v>
+      </c>
       <c r="M9" t="n">
-        <v>-5</v>
+        <v>-6.5</v>
       </c>
     </row>
   </sheetData>
@@ -1365,25 +1478,25 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="G2" t="n">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="H2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I2" t="n">
-        <v>23.5</v>
+        <v>23.3</v>
       </c>
       <c r="J2" t="n">
-        <v>20.5</v>
+        <v>21.7</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="3">
@@ -1408,25 +1521,25 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="G3" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="H3" t="n">
-        <v>-5</v>
+        <v>19</v>
       </c>
       <c r="I3" t="n">
-        <v>19</v>
+        <v>23.3</v>
       </c>
       <c r="J3" t="n">
-        <v>21.5</v>
+        <v>17</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.5</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="4">
@@ -1451,25 +1564,25 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="G4" t="n">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="H4" t="n">
-        <v>-8</v>
+        <v>-4</v>
       </c>
       <c r="I4" t="n">
-        <v>17</v>
+        <v>19.3</v>
       </c>
       <c r="J4" t="n">
-        <v>21</v>
+        <v>20.7</v>
       </c>
       <c r="K4" t="n">
-        <v>-4</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="5">
@@ -1494,25 +1607,25 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="G5" t="n">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="H5" t="n">
-        <v>-9</v>
+        <v>-12</v>
       </c>
       <c r="I5" t="n">
-        <v>19.5</v>
+        <v>21.3</v>
       </c>
       <c r="J5" t="n">
-        <v>24</v>
+        <v>25.3</v>
       </c>
       <c r="K5" t="n">
-        <v>-4.5</v>
+        <v>-4</v>
       </c>
     </row>
   </sheetData>
@@ -1639,111 +1752,111 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. Morgan</t>
+          <t>P. Nixon</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="E2" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="H2" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="I2" t="n">
-        <v>2.5</v>
+        <v>0.3</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="O2" t="n">
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. Nixon</t>
+          <t>M. Morgan</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="E3" t="n">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L3" t="n">
         <v>2</v>
       </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
       <c r="M3" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="4">
@@ -1756,49 +1869,49 @@
         <v>4</v>
       </c>
       <c r="C4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F4" t="n">
         <v>2</v>
       </c>
-      <c r="D4" t="n">
+      <c r="G4" t="n">
         <v>1</v>
       </c>
-      <c r="E4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.5</v>
-      </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="I4" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="5">
@@ -1811,40 +1924,40 @@
         <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
         <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1863,28 +1976,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="C6" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="F6" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1902,7 +2015,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -1918,25 +2031,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="C7" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" t="n">
         <v>1</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="G7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.5</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
@@ -1945,22 +2058,22 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1973,52 +2086,52 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="C8" t="n">
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="L8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="P8" t="n">
         <v>1</v>
       </c>
-      <c r="M8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.5</v>
-      </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="9">
@@ -2028,52 +2141,52 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="L9" t="n">
         <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
     </row>
   </sheetData>
@@ -2088,11 +2201,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -2195,8 +2308,37 @@
         <v>-25</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2922738</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Esgueira Aveiro OLI</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>104</v>
+      </c>
+      <c r="F4" t="n">
+        <v>80</v>
+      </c>
+      <c r="G4" t="n">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G3"/>
+  <autoFilter ref="A1:G4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>